--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>68135879</v>
       </c>
       <c r="B7" t="n">
-        <v>99141</v>
+        <v>99454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,11 +1338,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>68135879</v>
       </c>
       <c r="B7" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>68135879</v>
       </c>
       <c r="B7" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
